--- a/CALCULATOR_Testcase.xlsx
+++ b/CALCULATOR_Testcase.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GAURI\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1A446F-1F55-4D09-8951-48E17E6462AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -21,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -137,6 +131,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Click on </t>
     </r>
@@ -146,6 +141,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Submit</t>
     </r>
@@ -154,6 +150,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> button</t>
     </r>
@@ -168,6 +165,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Enter the received OTP and click on </t>
     </r>
@@ -177,6 +175,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Verify</t>
     </r>
@@ -194,6 +193,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Click on </t>
     </r>
@@ -203,6 +203,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Submit</t>
     </r>
@@ -211,6 +212,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> button</t>
     </r>
@@ -228,6 +230,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Click on </t>
     </r>
@@ -237,6 +240,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Submit</t>
     </r>
@@ -245,6 +249,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> button</t>
     </r>
@@ -269,24 +274,6 @@
     <t xml:space="preserve">1.0 </t>
   </si>
   <si>
-    <t xml:space="preserve"> Verify that the calculator perform all Mathematical Calculations.</t>
-  </si>
-  <si>
-    <t>System Availability</t>
-  </si>
-  <si>
-    <t>User Access</t>
-  </si>
-  <si>
-    <t>Hardware/Software</t>
-  </si>
-  <si>
-    <t>Open the Calculator Application from the Start Menu.</t>
-  </si>
-  <si>
-    <t>Calculator Application Open Successfully</t>
-  </si>
-  <si>
     <t>Enter 10+5 and click =</t>
   </si>
   <si>
@@ -309,9 +296,6 @@
   </si>
   <si>
     <t>Enter 7/2  and click =</t>
-  </si>
-  <si>
-    <t>The last entered digit is deleted</t>
   </si>
   <si>
     <t xml:space="preserve">Enter values,then press C </t>
@@ -359,9 +343,6 @@
     <t xml:space="preserve">Close the calculator by clicking the (x) button. </t>
   </si>
   <si>
-    <t>Calculator Application Close  Successfully.</t>
-  </si>
-  <si>
     <t>Calculator opens and functions properly.</t>
   </si>
   <si>
@@ -375,9 +356,6 @@
   </si>
   <si>
     <t>Perform a calculation and press the MR (memory recall)button.</t>
-  </si>
-  <si>
-    <t>Values is Recall in MR button.</t>
   </si>
   <si>
     <t xml:space="preserve">Perform a calculation and press the M (memory)button. </t>
@@ -398,26 +376,50 @@
     <t>Press the backspace key after entering a number.</t>
   </si>
   <si>
-    <t>Displayed the message is "Cannot divide by zero".</t>
-  </si>
-  <si>
-    <t>Test the Functionality of Windows Calculator Application</t>
-  </si>
-  <si>
     <t>Bhavana Mahalle</t>
   </si>
   <si>
     <t>TC_Practical-002</t>
   </si>
+  <si>
+    <t xml:space="preserve">  Test entire functionality of Calculator Application.</t>
+  </si>
+  <si>
+    <t>Verify that the last entered digit is deleted</t>
+  </si>
+  <si>
+    <t>Verify that displayed the message is "Cannot divide by zero".</t>
+  </si>
+  <si>
+    <t>Windows OS</t>
+  </si>
+  <si>
+    <t>Calculator application</t>
+  </si>
+  <si>
+    <t>Test the functionality of simple calculator application.</t>
+  </si>
+  <si>
+    <t>Values is recall in MR button.</t>
+  </si>
+  <si>
+    <t>Open the calculator application from the Start menu.</t>
+  </si>
+  <si>
+    <t>Calculator Application closed  successfully.</t>
+  </si>
+  <si>
+    <t>Calculator application opened successfully</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -429,15 +431,18 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -445,18 +450,46 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -792,7 +825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -866,81 +899,164 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -964,22 +1080,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>109469</xdr:colOff>
+      <xdr:colOff>242819</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>682196</xdr:rowOff>
+      <xdr:rowOff>493241</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>855347</xdr:colOff>
+      <xdr:colOff>988697</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>1769848</xdr:rowOff>
+      <xdr:rowOff>1580893</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A6670D4-351E-A0F4-7791-37342E96CD64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7A6670D4-351E-A0F4-7791-37342E96CD64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -996,8 +1112,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2329824" y="3121368"/>
-          <a:ext cx="1775607" cy="1087652"/>
+          <a:off x="2462144" y="3674591"/>
+          <a:ext cx="1774578" cy="1087652"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1211,7 +1327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y994"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1224,10 +1340,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
+      <c r="B1" s="26"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1235,13 +1351,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1259,10 +1375,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="31"/>
       <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1273,11 +1389,11 @@
       <c r="F2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="45" t="s">
+      <c r="G2" s="31"/>
+      <c r="H2" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1298,10 +1414,10 @@
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1309,14 +1425,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="54">
+      <c r="F3" s="34">
         <v>46220</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="45" t="s">
+      <c r="G3" s="31"/>
+      <c r="H3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="33"/>
+      <c r="I3" s="31"/>
       <c r="J3" s="9" t="s">
         <v>14</v>
       </c>
@@ -1367,21 +1483,21 @@
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="33"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="31"/>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="36"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1405,8 +1521,8 @@
       <c r="B6" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="33"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="31"/>
       <c r="E6" s="5"/>
       <c r="F6" s="17">
         <v>1</v>
@@ -1414,9 +1530,9 @@
       <c r="G6" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="36"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1440,8 +1556,8 @@
       <c r="B7" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="33"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="31"/>
       <c r="E7" s="5"/>
       <c r="F7" s="17">
         <v>2</v>
@@ -1449,9 +1565,9 @@
       <c r="G7" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="36"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1473,16 +1589,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="32"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="5"/>
       <c r="F8" s="17">
         <v>3</v>
       </c>
       <c r="G8" s="32"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="36"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1503,17 +1619,17 @@
       <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="41"/>
       <c r="K9" s="21"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1561,17 +1677,17 @@
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1590,17 +1706,17 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1648,23 +1764,23 @@
       <c r="A14" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="36" t="s">
+      <c r="C14" s="26"/>
+      <c r="D14" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="36" t="s">
+      <c r="E14" s="26"/>
+      <c r="F14" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="36" t="s">
+      <c r="G14" s="28"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="39"/>
+      <c r="J14" s="29"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1685,23 +1801,23 @@
       <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="33"/>
+      <c r="C15" s="31"/>
       <c r="D15" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="33"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="33"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="35"/>
+      <c r="J15" s="36"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1725,20 +1841,20 @@
       <c r="B16" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="33"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="33"/>
+      <c r="E16" s="31"/>
       <c r="F16" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="33"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="31"/>
       <c r="I16" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="35"/>
+      <c r="J16" s="36"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1762,20 +1878,20 @@
       <c r="B17" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="33"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="33"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="33"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="35"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1799,20 +1915,20 @@
       <c r="B18" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="33"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="33"/>
+      <c r="E18" s="31"/>
       <c r="F18" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="33"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="31"/>
       <c r="I18" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="35"/>
+      <c r="J18" s="36"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -1836,20 +1952,20 @@
       <c r="B19" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="33"/>
+      <c r="C19" s="31"/>
       <c r="D19" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="33"/>
+      <c r="E19" s="31"/>
       <c r="F19" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="33"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="31"/>
       <c r="I19" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="35"/>
+      <c r="J19" s="36"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -1873,20 +1989,20 @@
       <c r="B20" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="33"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="33"/>
+      <c r="E20" s="31"/>
       <c r="F20" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="33"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="31"/>
       <c r="I20" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="35"/>
+      <c r="J20" s="36"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -1910,20 +2026,20 @@
       <c r="B21" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="33"/>
+      <c r="C21" s="31"/>
       <c r="D21" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="33"/>
+      <c r="E21" s="31"/>
       <c r="F21" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="33"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="31"/>
       <c r="I21" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="35"/>
+      <c r="J21" s="36"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -1947,20 +2063,20 @@
       <c r="B22" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="33"/>
+      <c r="C22" s="31"/>
       <c r="D22" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="33"/>
+      <c r="E22" s="31"/>
       <c r="F22" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="33"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="31"/>
       <c r="I22" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="35"/>
+      <c r="J22" s="36"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -1982,14 +2098,14 @@
         <v>9</v>
       </c>
       <c r="B23" s="32"/>
-      <c r="C23" s="33"/>
+      <c r="C23" s="31"/>
       <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
+      <c r="E23" s="31"/>
       <c r="F23" s="32"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="33"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="31"/>
       <c r="I23" s="32"/>
-      <c r="J23" s="35"/>
+      <c r="J23" s="36"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2011,14 +2127,14 @@
         <v>10</v>
       </c>
       <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
+      <c r="C24" s="31"/>
       <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
+      <c r="E24" s="31"/>
       <c r="F24" s="32"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="33"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="31"/>
       <c r="I24" s="32"/>
-      <c r="J24" s="35"/>
+      <c r="J24" s="36"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2040,14 +2156,14 @@
         <v>11</v>
       </c>
       <c r="B25" s="32"/>
-      <c r="C25" s="33"/>
+      <c r="C25" s="31"/>
       <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
+      <c r="E25" s="31"/>
       <c r="F25" s="32"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="33"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="31"/>
       <c r="I25" s="32"/>
-      <c r="J25" s="35"/>
+      <c r="J25" s="36"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2069,14 +2185,14 @@
         <v>12</v>
       </c>
       <c r="B26" s="32"/>
-      <c r="C26" s="33"/>
+      <c r="C26" s="31"/>
       <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
+      <c r="E26" s="31"/>
       <c r="F26" s="32"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="33"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="31"/>
       <c r="I26" s="32"/>
-      <c r="J26" s="35"/>
+      <c r="J26" s="36"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2098,14 +2214,14 @@
         <v>13</v>
       </c>
       <c r="B27" s="32"/>
-      <c r="C27" s="33"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
+      <c r="E27" s="31"/>
       <c r="F27" s="32"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="33"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="31"/>
       <c r="I27" s="32"/>
-      <c r="J27" s="35"/>
+      <c r="J27" s="36"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2127,14 +2243,14 @@
         <v>14</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="33"/>
+      <c r="C28" s="31"/>
       <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="32"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="33"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="31"/>
       <c r="I28" s="32"/>
-      <c r="J28" s="35"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2156,14 +2272,14 @@
         <v>15</v>
       </c>
       <c r="B29" s="32"/>
-      <c r="C29" s="33"/>
+      <c r="C29" s="31"/>
       <c r="D29" s="32"/>
-      <c r="E29" s="33"/>
+      <c r="E29" s="31"/>
       <c r="F29" s="32"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="33"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="31"/>
       <c r="I29" s="32"/>
-      <c r="J29" s="35"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2185,14 +2301,14 @@
         <v>16</v>
       </c>
       <c r="B30" s="32"/>
-      <c r="C30" s="33"/>
+      <c r="C30" s="31"/>
       <c r="D30" s="32"/>
-      <c r="E30" s="33"/>
+      <c r="E30" s="31"/>
       <c r="F30" s="32"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="33"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="32"/>
-      <c r="J30" s="35"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2214,14 +2330,14 @@
         <v>17</v>
       </c>
       <c r="B31" s="32"/>
-      <c r="C31" s="33"/>
+      <c r="C31" s="31"/>
       <c r="D31" s="32"/>
-      <c r="E31" s="33"/>
+      <c r="E31" s="31"/>
       <c r="F31" s="32"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="33"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="31"/>
       <c r="I31" s="32"/>
-      <c r="J31" s="35"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2243,14 +2359,14 @@
         <v>18</v>
       </c>
       <c r="B32" s="32"/>
-      <c r="C32" s="33"/>
+      <c r="C32" s="31"/>
       <c r="D32" s="32"/>
-      <c r="E32" s="33"/>
+      <c r="E32" s="31"/>
       <c r="F32" s="32"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="33"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="31"/>
       <c r="I32" s="32"/>
-      <c r="J32" s="35"/>
+      <c r="J32" s="36"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2272,14 +2388,14 @@
         <v>19</v>
       </c>
       <c r="B33" s="32"/>
-      <c r="C33" s="33"/>
+      <c r="C33" s="31"/>
       <c r="D33" s="32"/>
-      <c r="E33" s="33"/>
+      <c r="E33" s="31"/>
       <c r="F33" s="32"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="33"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="31"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="35"/>
+      <c r="J33" s="36"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2300,15 +2416,15 @@
       <c r="A34" s="18">
         <v>20</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="31"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="41"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -28247,38 +28363,54 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="B25:C25"/>
@@ -28303,57 +28435,41 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B15" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B15" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -28361,767 +28477,801 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J43"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="8" max="8" width="1.28515625" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" style="55" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="55"/>
+    <col min="3" max="3" width="16.5703125" style="55" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="55" customWidth="1"/>
+    <col min="5" max="5" width="20" style="55" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="55"/>
+    <col min="7" max="7" width="7.42578125" style="55" customWidth="1"/>
+    <col min="8" max="8" width="1.28515625" style="55" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="55" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" style="55" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="56" t="s">
-        <v>97</v>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49" t="s">
+        <v>86</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="48" t="s">
+      <c r="E1" s="51"/>
+      <c r="F1" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="54"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="57"/>
+      <c r="H2" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="57"/>
+      <c r="J2" s="63" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="60"/>
+      <c r="F3" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="57"/>
+      <c r="H3" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="57"/>
+      <c r="J3" s="65" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="68"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="74"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="75">
+        <v>1</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="71"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="76">
+        <v>1</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="74"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>2</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="71"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="76">
+        <v>2</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="74"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="75">
+        <v>3</v>
+      </c>
+      <c r="B8" s="61"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="76">
+        <v>3</v>
+      </c>
+      <c r="G8" s="61"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="74"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="77">
+        <v>4</v>
+      </c>
+      <c r="B9" s="78"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="82">
+        <v>4</v>
+      </c>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="83"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="84"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
+    </row>
+    <row r="11" spans="1:10" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="87"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="88"/>
+      <c r="B12" s="89" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="88"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88"/>
+    </row>
+    <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="48"/>
+      <c r="D14" s="91" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="48"/>
+      <c r="F14" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="53"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="54"/>
+    </row>
+    <row r="15" spans="1:10" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <v>1</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="57"/>
+      <c r="D15" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="57"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="74"/>
+    </row>
+    <row r="16" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <v>2</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="57"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="74"/>
+    </row>
+    <row r="17" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <v>3</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="57"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="74"/>
+    </row>
+    <row r="18" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <v>4</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="57"/>
+      <c r="D18" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="57"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="74"/>
+    </row>
+    <row r="19" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>5</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="57"/>
+      <c r="D19" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="57"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="74"/>
+    </row>
+    <row r="20" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <v>6</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="57"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="74"/>
+    </row>
+    <row r="21" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <v>7</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="57"/>
+      <c r="D21" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="57"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="74"/>
+    </row>
+    <row r="22" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <v>8</v>
+      </c>
+      <c r="B22" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="57"/>
+      <c r="D22" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="57"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="74"/>
+    </row>
+    <row r="23" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <v>9</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="57"/>
+      <c r="D23" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="57"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="74"/>
+    </row>
+    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <v>10</v>
+      </c>
+      <c r="B24" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="57"/>
+      <c r="D24" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="57"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="74"/>
+    </row>
+    <row r="25" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <v>11</v>
+      </c>
+      <c r="B25" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="57"/>
+      <c r="D25" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="57"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="74"/>
+    </row>
+    <row r="26" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <v>12</v>
+      </c>
+      <c r="B26" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="57"/>
+      <c r="D26" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="57"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="74"/>
+    </row>
+    <row r="27" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <v>13</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="57"/>
+      <c r="D27" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="57"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="74"/>
+    </row>
+    <row r="28" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <v>14</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="57"/>
+      <c r="D28" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="57"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="74"/>
+    </row>
+    <row r="29" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <v>15</v>
+      </c>
+      <c r="B29" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="57"/>
+      <c r="D29" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="57"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="74"/>
+    </row>
+    <row r="30" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <v>16</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="57"/>
+      <c r="D30" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="57"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="74"/>
+    </row>
+    <row r="31" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <v>17</v>
+      </c>
+      <c r="B31" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="57"/>
+      <c r="D31" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="57"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="74"/>
+    </row>
+    <row r="32" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <v>18</v>
+      </c>
+      <c r="B32" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="57"/>
+      <c r="D32" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="57"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="74"/>
+    </row>
+    <row r="33" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <v>19</v>
+      </c>
+      <c r="B33" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="57"/>
+      <c r="D33" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="57"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="74"/>
+    </row>
+    <row r="34" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="77">
+        <v>20</v>
+      </c>
+      <c r="B34" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="80"/>
+      <c r="D34" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="33"/>
-      <c r="J2" s="26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="33"/>
-      <c r="J3" s="27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="12"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
-        <v>1</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="17">
-        <v>1</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="16">
-        <v>2</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="17">
-        <v>2</v>
-      </c>
-      <c r="G7" s="46" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="35"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
-        <v>3</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="17">
-        <v>3</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="35"/>
-    </row>
-    <row r="9" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
-        <v>4</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20">
-        <v>4</v>
-      </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-    </row>
-    <row r="11" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-    </row>
-    <row r="13" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="39"/>
-    </row>
-    <row r="15" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="16">
-        <v>1</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="35"/>
-    </row>
-    <row r="16" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
-        <v>2</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="35"/>
-    </row>
-    <row r="17" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16">
-        <v>3</v>
-      </c>
-      <c r="B17" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="35"/>
-    </row>
-    <row r="18" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
-        <v>4</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="35"/>
-    </row>
-    <row r="19" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="16">
-        <v>5</v>
-      </c>
-      <c r="B19" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="35"/>
-    </row>
-    <row r="20" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16">
-        <v>6</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="35"/>
-    </row>
-    <row r="21" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="16">
-        <v>7</v>
-      </c>
-      <c r="B21" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="35"/>
-    </row>
-    <row r="22" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16">
-        <v>8</v>
-      </c>
-      <c r="B22" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="35"/>
-    </row>
-    <row r="23" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="16">
-        <v>9</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="35"/>
-    </row>
-    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16">
-        <v>10</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="35"/>
-    </row>
-    <row r="25" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16">
-        <v>11</v>
-      </c>
-      <c r="B25" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="35"/>
-    </row>
-    <row r="26" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16">
-        <v>12</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="35"/>
-    </row>
-    <row r="27" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="16">
-        <v>13</v>
-      </c>
-      <c r="B27" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="35"/>
-    </row>
-    <row r="28" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="16">
-        <v>14</v>
-      </c>
-      <c r="B28" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="35"/>
-    </row>
-    <row r="29" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="16">
-        <v>15</v>
-      </c>
-      <c r="B29" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="33"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="35"/>
-    </row>
-    <row r="30" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="16">
-        <v>16</v>
-      </c>
-      <c r="B30" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="35"/>
-    </row>
-    <row r="31" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="16">
-        <v>17</v>
-      </c>
-      <c r="B31" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="35"/>
-    </row>
-    <row r="32" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16">
-        <v>18</v>
-      </c>
-      <c r="B32" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="33"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="35"/>
-    </row>
-    <row r="33" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="16">
-        <v>19</v>
-      </c>
-      <c r="B33" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="35"/>
-    </row>
-    <row r="34" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18">
-        <v>20</v>
-      </c>
-      <c r="B34" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="55" t="s">
-        <v>81</v>
-      </c>
-      <c r="E34" s="29"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="31"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="78"/>
+      <c r="J34" s="83"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="88"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="88"/>
+      <c r="I35" s="88"/>
+      <c r="J35" s="88"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="88"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="88"/>
+      <c r="E36" s="88"/>
+      <c r="F36" s="88"/>
+      <c r="G36" s="88"/>
+      <c r="H36" s="88"/>
+      <c r="I36" s="88"/>
+      <c r="J36" s="88"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="88"/>
+      <c r="B37" s="88"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="88"/>
+      <c r="B38" s="88"/>
+      <c r="C38" s="88"/>
+      <c r="D38" s="88"/>
+      <c r="E38" s="88"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="88"/>
+      <c r="H38" s="88"/>
+      <c r="I38" s="88"/>
+      <c r="J38" s="88"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="88"/>
+      <c r="B39" s="88"/>
+      <c r="C39" s="88"/>
+      <c r="D39" s="88"/>
+      <c r="E39" s="88"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="88"/>
+      <c r="H39" s="88"/>
+      <c r="I39" s="88"/>
+      <c r="J39" s="88"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="88"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
+      <c r="E40" s="88"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="88"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88"/>
+      <c r="J40" s="88"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="88"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="88"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="88"/>
+      <c r="F42" s="88"/>
+      <c r="G42" s="88"/>
+      <c r="H42" s="88"/>
+      <c r="I42" s="88"/>
+      <c r="J42" s="88"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="88"/>
+      <c r="B43" s="88"/>
+      <c r="C43" s="88"/>
+      <c r="D43" s="88"/>
+      <c r="E43" s="88"/>
+      <c r="F43" s="88"/>
+      <c r="G43" s="88"/>
+      <c r="H43" s="88"/>
+      <c r="I43" s="88"/>
+      <c r="J43" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:H18"/>
@@ -29138,69 +29288,37 @@
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>